--- a/data/output/authors_junk_names_elastic.xlsx
+++ b/data/output/authors_junk_names_elastic.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:M101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,21 +477,26 @@
           <t>name_source</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>belongs_to</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-11-17T00:24:21Z</t>
+          <t>2025-11-15T12:04:28Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054071']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032435']</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['scipo', 'eco']</t>
+          <t>['geo', 'demo']</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -499,17 +504,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>161278</t>
+          <t>123598</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>161278</t>
+          <t>123598</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>__-RiGMyAZFn88JM9bl_qH6</t>
+          <t>__-76q-D_tyR-oRhWq8F96z</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -526,42 +531,47 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>佐藤, 峰司</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-11-14T19:02:39Z</t>
+          <t>2025-11-17T00:30:49Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00004456']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017111']</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['stat', 'envir']</t>
+          <t>['edu', 'socio']</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>107580</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48473</t>
+          <t>107580</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>__-DakzhbtGCHwIR_92QEOF</t>
+          <t>__-D4-cr1sfD3mVHO5WDyjB</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -578,42 +588,47 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>久本, 貴志</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-11-15T12:04:28Z</t>
+          <t>2025-11-14T19:02:39Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032435']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00004456']</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['geo', 'demo']</t>
+          <t>['stat', 'envir']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>123598</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>123598</t>
+          <t>48473</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>__-76q-D_tyR-oRhWq8F96z</t>
+          <t>__-DakzhbtGCHwIR_92QEOF</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -630,7 +645,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>蘆田, 一郎</t>
         </is>
       </c>
     </row>
@@ -682,24 +702,29 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ハスバガン</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-11-17T00:30:49Z</t>
+          <t>2025-11-17T00:24:21Z</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017111']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054071']</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['edu', 'socio']</t>
+          <t>['scipo', 'eco']</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -707,17 +732,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>107580</t>
+          <t>161278</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>107580</t>
+          <t>161278</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>__-D4-cr1sfD3mVHO5WDyjB</t>
+          <t>__-RiGMyAZFn88JM9bl_qH6</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -734,7 +759,12 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>増田, 康介</t>
         </is>
       </c>
     </row>
@@ -786,7 +816,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>下保, 敏和</t>
         </is>
       </c>
     </row>
@@ -838,7 +873,12 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Ogimoto, Kazuhiko</t>
         </is>
       </c>
     </row>
@@ -890,24 +930,29 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>斉藤, こずゑ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-16T22:24:33Z</t>
+          <t>2025-11-15T00:25:19Z</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051183']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025263']</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['lang', 'art']</t>
+          <t>['geo', 'demo']</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -915,17 +960,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>152231</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>152231</t>
+          <t>149415</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>__-jAvurCrgF1fPdAxeXxZc</t>
+          <t>__-fkd_cA0QJw1BJBwp9Mjx</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -942,24 +987,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>大木, 靖衛</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-15T00:25:19Z</t>
+          <t>2025-11-16T22:24:33Z</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025263']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051183']</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['geo', 'demo']</t>
+          <t>['lang', 'art']</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -967,17 +1017,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>149415</t>
+          <t>152231</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>149415</t>
+          <t>152231</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>__-fkd_cA0QJw1BJBwp9Mjx</t>
+          <t>__-jAvurCrgF1fPdAxeXxZc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -994,24 +1044,29 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>野中, 大輔</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-14T22:19:08Z</t>
+          <t>2025-11-15T06:26:57Z</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031456']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026490']</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['hist', 'edu']</t>
+          <t>['edu', 'info']</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1019,17 +1074,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>123423</t>
+          <t>156154</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>123423</t>
+          <t>156154</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>__-wrcvuS2J1L2RhHKJLKKw</t>
+          <t>__-u0mJprVc5inyht_BSzyf</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1046,24 +1101,29 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>早川, 潤</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-15T06:26:57Z</t>
+          <t>2025-11-14T22:19:08Z</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00026490']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031456']</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['edu', 'info']</t>
+          <t>['hist', 'edu']</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1071,17 +1131,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>156154</t>
+          <t>123423</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>156154</t>
+          <t>123423</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>__-u0mJprVc5inyht_BSzyf</t>
+          <t>__-wrcvuS2J1L2RhHKJLKKw</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -1098,47 +1158,52 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>金井, 香里</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-15T12:04:28Z</t>
+          <t>2025-11-15T13:26:44Z</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032435']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001810', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001891']</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['geo', 'demo']</t>
+          <t>['info', 'lang', 'museo']</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>123591</t>
+          <t>5445</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>__09bcXj0mNuqHebIN8xXnk</t>
+          <t>__-xAe5m-aP9NkyX4pc-Kfq</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1150,24 +1215,29 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Shinoda, Shoji</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-16T23:44:46Z</t>
+          <t>2025-11-15T12:04:28Z</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025846']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032435']</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['genre', 'manag']</t>
+          <t>['geo', 'demo']</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1175,17 +1245,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>152498</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>152498</t>
+          <t>123591</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>__0TacCzOZUNzwVUxXSPv4U</t>
+          <t>__09bcXj0mNuqHebIN8xXnk</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
@@ -1202,47 +1272,52 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>森田, 裕一</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-15T13:26:44Z</t>
+          <t>2025-11-16T23:44:46Z</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001810', 'ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001891']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025846']</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['info', 'lang', 'museo']</t>
+          <t>['genre', 'manag']</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>152498</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>152498</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>__-xAe5m-aP9NkyX4pc-Kfq</t>
+          <t>__0TacCzOZUNzwVUxXSPv4U</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
@@ -1254,24 +1329,29 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>今井, 信行</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-11-16T05:22:57Z</t>
+          <t>2025-11-14T19:01:15Z</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00017470']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00022607']</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['socio', 'lang']</t>
+          <t>['stat', 'edu']</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1279,17 +1359,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>110199</t>
+          <t>137169</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>110199</t>
+          <t>137169</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>__0oWNI86bByUPnlbJSnXyA</t>
+          <t>__0bWeDiV2cfbVb8FUmBwzz</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
@@ -1306,42 +1386,47 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>遠藤, 和男</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-11-15T04:07:27Z</t>
+          <t>2025-11-17T03:24:39Z</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017733']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00029261']</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['scipo', 'droit']</t>
+          <t>['info', 'edu']</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>28549</t>
+          <t>165679</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>__116QaQC8klVnfrm2qeKoi</t>
+          <t>__0lBlhpxa_25RZy8hqSNNY</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1358,24 +1443,29 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>伊藤, 紀美子</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-11-14T19:01:15Z</t>
+          <t>2025-11-16T05:22:57Z</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00022607']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00017470']</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['stat', 'edu']</t>
+          <t>['socio', 'lang']</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1383,17 +1473,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>110199</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>137169</t>
+          <t>110199</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>__0bWeDiV2cfbVb8FUmBwzz</t>
+          <t>__0oWNI86bByUPnlbJSnXyA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
@@ -1410,42 +1500,47 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>熊木, 克治</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-11-15T19:29:12Z</t>
+          <t>2025-11-15T04:07:27Z</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031464']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017733']</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['socio', 'edu']</t>
+          <t>['scipo', 'droit']</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>__1VQTJ2k2UZXUm0hrnx7Jx</t>
+          <t>__116QaQC8klVnfrm2qeKoi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
@@ -1462,24 +1557,29 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>廣川, 祐司</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:39Z</t>
+          <t>2025-11-15T19:29:12Z</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00029261']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031464']</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['info', 'edu']</t>
+          <t>['socio', 'edu']</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1487,17 +1587,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>165679</t>
+          <t>123439</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>165679</t>
+          <t>123439</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>__0lBlhpxa_25RZy8hqSNNY</t>
+          <t>__1VQTJ2k2UZXUm0hrnx7Jx</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
@@ -1514,7 +1614,12 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>伊藤, 真木子</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1671,12 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>張, 晨迪</t>
         </is>
       </c>
     </row>
@@ -1618,7 +1728,12 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Nadai, A.</t>
         </is>
       </c>
     </row>
@@ -1670,42 +1785,47 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Kuno, Masakazu</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2025-11-17T02:09:54Z</t>
+          <t>2025-11-15T13:26:43Z</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00048959']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001811']</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['info', 'geo']</t>
+          <t>['envir', 'info']</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>145483</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>145483</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>__2SK_i7NX7GZATbr3cKBj1</t>
+          <t>__2FnOotKSr5z4FmCrbxIlv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -1722,42 +1842,47 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Bilhaj, Abdulkhalig A.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2025-11-16T23:44:46Z</t>
+          <t>2025-11-15T12:05:07Z</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025846']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017053']</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['genre', 'manag']</t>
+          <t>['manag', 'eco']</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>152492</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>152492</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>__2VoVJpnAgGTATiwwlOJ2j</t>
+          <t>__2Qx523Q8dBZ27RGkSiNNF</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1774,24 +1899,29 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>新海, 哲哉</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2025-11-14T19:01:28Z</t>
+          <t>2025-11-17T02:09:54Z</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00048959']</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>['socio', 'envir']</t>
+          <t>['info', 'geo']</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1799,17 +1929,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>162516</t>
+          <t>145483</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>162516</t>
+          <t>145483</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>__2gA6WcTnqv6r4D-ILewo9</t>
+          <t>__2SK_i7NX7GZATbr3cKBj1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
@@ -1826,42 +1956,47 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>IMAI, Hiroshi</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2025-11-15T13:26:43Z</t>
+          <t>2025-11-16T23:44:46Z</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001811']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025846']</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>['envir', 'info']</t>
+          <t>['genre', 'manag']</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>152492</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>152492</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>__2FnOotKSr5z4FmCrbxIlv</t>
+          <t>__2VoVJpnAgGTATiwwlOJ2j</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
@@ -1878,42 +2013,47 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>碓井, 由紀子</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2025-11-15T12:05:07Z</t>
+          <t>2025-11-14T19:01:28Z</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017053']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['manag', 'eco']</t>
+          <t>['socio', 'envir']</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>162516</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>162516</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>__2Qx523Q8dBZ27RGkSiNNF</t>
+          <t>__2gA6WcTnqv6r4D-ILewo9</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
@@ -1930,7 +2070,12 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ebe, Yusuke</t>
         </is>
       </c>
     </row>
@@ -1982,7 +2127,12 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>神田, 知哉</t>
         </is>
       </c>
     </row>
@@ -2034,42 +2184,47 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>中石, 誠子</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2025-11-15T00:33:28Z</t>
+          <t>2025-11-17T02:09:54Z</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003640']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>['envir', 'socio']</t>
+          <t>['lang', 'edu']</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>160112</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>44249</t>
+          <t>160112</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>__3OYzeNCpgom0Tu3HPSAzj</t>
+          <t>__2s6KcJyR8Ug42-PftPEwK</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -2086,24 +2241,29 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>宇田川, 敦史</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2025-11-17T02:09:54Z</t>
+          <t>2025-11-15T19:24:17Z</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051138']</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>['lang', 'edu']</t>
+          <t>['phil', 'socio']</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -2111,17 +2271,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>160112</t>
+          <t>152070</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>160112</t>
+          <t>152070</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>__2s6KcJyR8Ug42-PftPEwK</t>
+          <t>__2vGBRrxTT1aDKdOtxprGA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
@@ -2138,42 +2298,47 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>石神, 真悠子</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2025-11-15T19:24:17Z</t>
+          <t>2025-11-15T12:05:06Z</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051138']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00001632']</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>['phil', 'socio']</t>
+          <t>['info', 'manag']</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>152070</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>152070</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>__2vGBRrxTT1aDKdOtxprGA</t>
+          <t>__2z0ESltr0nJ9et615vyFs</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -2190,24 +2355,29 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Tran, Quang Trung</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2025-11-15T12:05:06Z</t>
+          <t>2025-11-17T03:24:53Z</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00001632']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002056']</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>['info', 'manag']</t>
+          <t>['geo', 'socio']</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -2215,17 +2385,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>__2z0ESltr0nJ9et615vyFs</t>
+          <t>__3E7yPJw2sIc6jzo9J7wF3</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -2242,42 +2412,47 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Harada, Naoki</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:53Z</t>
+          <t>2025-11-15T00:33:28Z</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002056']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003640']</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>['geo', 'socio']</t>
+          <t>['envir', 'socio']</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>44249</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>__3E7yPJw2sIc6jzo9J7wF3</t>
+          <t>__3OYzeNCpgom0Tu3HPSAzj</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
@@ -2294,7 +2469,12 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>長沢, 由喜子</t>
         </is>
       </c>
     </row>
@@ -2346,24 +2526,29 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>坂井, 菜央美</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2025-11-14T19:01:28Z</t>
+          <t>2025-11-14T18:57:22Z</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028304']</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>['socio', 'envir']</t>
+          <t>['envir', 'socio']</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2371,17 +2556,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>162514</t>
+          <t>162679</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>162514</t>
+          <t>162679</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>__3QVi7Fra7hZBxwp0snWb3</t>
+          <t>__3QQf-7gboYXMxC4-V4966</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -2398,42 +2583,47 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Kawanabe, Takahiro</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2025-11-14T22:54:24Z</t>
+          <t>2025-11-14T19:01:28Z</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017029']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>['phil', 'demo']</t>
+          <t>['socio', 'envir']</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>162514</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>27165</t>
+          <t>162514</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>__3b_-lwrs3nP2_P92Jgd5r</t>
+          <t>__3QVi7Fra7hZBxwp0snWb3</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -2450,24 +2640,29 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Kawamura, Kazutaka</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2025-11-14T18:57:22Z</t>
+          <t>2025-11-16T16:17:41Z</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028304']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054616']</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>['envir', 'socio']</t>
+          <t>['scipo', 'hist']</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -2475,17 +2670,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>162679</t>
+          <t>162531</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>__3QQf-7gboYXMxC4-V4966</t>
+          <t>__3VFsX0b-3JronnekwvOsC</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -2502,42 +2697,47 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>礒山, 麻衣</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2025-11-17T02:09:54Z</t>
+          <t>2025-11-14T22:54:24Z</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017029']</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>['lang', 'edu']</t>
+          <t>['phil', 'demo']</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>27165</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>__3mEWrog6STQTFWDsOGk17</t>
+          <t>__3b_-lwrs3nP2_P92Jgd5r</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
@@ -2554,42 +2754,47 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>大堀, 研</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2025-11-16T16:17:41Z</t>
+          <t>2025-11-15T12:04:28Z</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054616']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032177']</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>['scipo', 'hist']</t>
+          <t>['geo', 'demo']</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>162531</t>
+          <t>71611</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>162531</t>
+          <t>71611</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>__3VFsX0b-3JronnekwvOsC</t>
+          <t>__3kfVVyEvyKKw6cGFs4krH</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -2606,42 +2811,47 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>植平, 賢司</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2025-11-15T12:04:28Z</t>
+          <t>2025-11-17T02:09:54Z</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032177']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00053950']</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>['geo', 'demo']</t>
+          <t>['lang', 'edu']</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>160114</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>71611</t>
+          <t>160114</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>__3kfVVyEvyKKw6cGFs4krH</t>
+          <t>__3mEWrog6STQTFWDsOGk17</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -2658,7 +2868,12 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>神谷, 説子</t>
         </is>
       </c>
     </row>
@@ -2710,42 +2925,47 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>遠藤, 和男</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:52Z</t>
+          <t>2025-11-15T19:30:47Z</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00029387']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030051']</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>['info', 'edu']</t>
+          <t>['hist', 'scipo']</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>165923</t>
+          <t>66160</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>165923</t>
+          <t>66160</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>__4Bf41knrAMEYb8wEKWBNH</t>
+          <t>__4349nkYB_czzXaDmtTdGg</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -2762,42 +2982,47 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>佐治, 守夫</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2025-11-15T00:19:04Z</t>
+          <t>2025-11-17T03:24:52Z</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00009219']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00029387']</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>['lang', 'socio']</t>
+          <t>['info', 'edu']</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>64119</t>
+          <t>165923</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>64119</t>
+          <t>165923</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>__4ghVt12c8kFmCahrZ3rpI</t>
+          <t>__4Bf41knrAMEYb8wEKWBNH</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
@@ -2814,24 +3039,29 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>山内, 志朗</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2025-11-15T19:30:47Z</t>
+          <t>2025-11-17T02:10:07Z</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030051']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041851']</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>['hist', 'scipo']</t>
+          <t>['edu', 'socio']</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2839,17 +3069,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>66160</t>
+          <t>96104</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>__4349nkYB_czzXaDmtTdGg</t>
+          <t>__4HmRRkEjk1Rd2vVd8SYpo</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -2866,42 +3096,47 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Entzinger, Jorg O.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2025-11-14T18:59:26Z</t>
+          <t>2025-11-15T19:24:06Z</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002637']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049291']</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>['demo', 'envir']</t>
+          <t>['socio', 'demo']</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>146274</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>146274</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>__4iZ1ELeFZVAiPharywH1W</t>
+          <t>__4KWp_zLIlczck1SADrVkN</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
@@ -2918,24 +3153,29 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>柳, 采延</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2025-11-17T02:10:07Z</t>
+          <t>2025-11-15T00:19:04Z</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041851']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00009219']</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>['edu', 'socio']</t>
+          <t>['lang', 'socio']</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2943,17 +3183,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>96104</t>
+          <t>64119</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>96104</t>
+          <t>64119</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>__4HmRRkEjk1Rd2vVd8SYpo</t>
+          <t>__4ghVt12c8kFmCahrZ3rpI</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -2970,42 +3210,47 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>森田, 由香</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2025-11-15T19:24:06Z</t>
+          <t>2025-11-14T18:59:26Z</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00049291']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00002637']</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>['socio', 'demo']</t>
+          <t>['demo', 'envir']</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>146274</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>146274</t>
+          <t>38261</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>__4KWp_zLIlczck1SADrVkN</t>
+          <t>__4iZ1ELeFZVAiPharywH1W</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
@@ -3022,42 +3267,47 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Kawamura, Kazuko</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2025-11-14T19:00:07Z</t>
+          <t>2025-11-17T03:24:53Z</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00005371']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>['demo', 'envir']</t>
+          <t>['info', 'lang']</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>152930</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>50167</t>
+          <t>152930</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>__4yRbZcM_eJC9Zxjv2tnvh</t>
+          <t>__4tyt86ZR5o5gBcaNSY7Lp</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
@@ -3074,24 +3324,29 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>林, 孝文</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2025-11-16T05:55:37Z</t>
+          <t>2025-11-14T19:01:28Z</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025509']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>['hisphilso', 'socio']</t>
+          <t>['socio', 'envir']</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -3099,17 +3354,17 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>150382</t>
+          <t>162515</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>150382</t>
+          <t>162515</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>__5Akb-aa-Kyiq4T-sIF024</t>
+          <t>__4uvYfpsJ9v4WwtFZbRCf9</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
@@ -3126,42 +3381,47 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Saeki, Natsumi</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:53Z</t>
+          <t>2025-11-14T19:00:07Z</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00005371']</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>['info', 'lang']</t>
+          <t>['demo', 'envir']</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>152930</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>152930</t>
+          <t>50167</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>__4tyt86ZR5o5gBcaNSY7Lp</t>
+          <t>__4yRbZcM_eJC9Zxjv2tnvh</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
@@ -3178,24 +3438,29 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Nakazawa, Akemi</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2025-11-14T19:01:28Z</t>
+          <t>2025-11-16T05:55:37Z</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028286']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025509']</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>['socio', 'envir']</t>
+          <t>['hisphilso', 'socio']</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -3203,17 +3468,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>162515</t>
+          <t>150382</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>162515</t>
+          <t>150382</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>__4uvYfpsJ9v4WwtFZbRCf9</t>
+          <t>__5Akb-aa-Kyiq4T-sIF024</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
@@ -3230,7 +3495,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>吉岡, 節子</t>
         </is>
       </c>
     </row>
@@ -3242,12 +3512,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017233']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017234']</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>['eco', 'manag']</t>
+          <t>['eco', 'scipo']</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -3255,17 +3525,17 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>107816</t>
+          <t>107820</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>107816</t>
+          <t>107820</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>__5doLNQgjurzzt_Yw4_eEI</t>
+          <t>__5Bdqyf3WN6y5dZC_KT2yF</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
@@ -3282,24 +3552,29 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>田中, 悟</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-11-15T12:05:31Z</t>
+          <t>2025-11-15T19:29:00Z</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017234']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00047447']</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>['eco', 'scipo']</t>
+          <t>['droit', 'hist']</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -3307,17 +3582,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>107820</t>
+          <t>161199</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>107820</t>
+          <t>161199</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>__5Bdqyf3WN6y5dZC_KT2yF</t>
+          <t>__5Q-IiV8E6yzxVtlYgBbOn</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
@@ -3334,24 +3609,29 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>金子, 敬明</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-11-15T19:29:00Z</t>
+          <t>2025-11-15T12:05:31Z</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00047447']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017233']</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>['droit', 'hist']</t>
+          <t>['eco', 'manag']</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -3359,17 +3639,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>161199</t>
+          <t>107816</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>161199</t>
+          <t>107816</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>__5Q-IiV8E6yzxVtlYgBbOn</t>
+          <t>__5doLNQgjurzzt_Yw4_eEI</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
@@ -3386,7 +3666,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>大川, 隆夫</t>
         </is>
       </c>
     </row>
@@ -3438,24 +3723,29 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>外山, 孚</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-11-14T17:52:47Z</t>
+          <t>2025-11-17T00:05:47Z</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051987']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016929']</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>['stat', 'manag']</t>
+          <t>['eco', 'manag']</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -3463,17 +3753,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>161182</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>155429</t>
+          <t>161182</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>__6GGiCudkQkFY7XtRODgVf</t>
+          <t>__62bpvpEz90Eft2DZzAk_P</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -3490,42 +3780,47 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>安田, 宏樹</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-11-17T00:05:47Z</t>
+          <t>2025-11-15T04:04:06Z</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00016929']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00043323']</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>['eco', 'manag']</t>
+          <t>['manag', 'art']</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>161182</t>
+          <t>99538</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>161182</t>
+          <t>99538</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>__62bpvpEz90Eft2DZzAk_P</t>
+          <t>__69sIAJvNOfH1I8BBvxAc-</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -3542,24 +3837,29 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>髙祖, 歩美</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:53Z</t>
+          <t>2025-11-14T17:52:47Z</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051987']</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>['info', 'lang']</t>
+          <t>['stat', 'manag']</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -3567,17 +3867,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>155429</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>152932</t>
+          <t>155429</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>__6WRYQymo4NUk-yvxYsyOm</t>
+          <t>__6GGiCudkQkFY7XtRODgVf</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
@@ -3594,42 +3894,47 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>山口, 一大</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-11-15T04:04:06Z</t>
+          <t>2025-11-17T03:24:53Z</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00043323']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>['manag', 'art']</t>
+          <t>['info', 'lang']</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>99538</t>
+          <t>152932</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>99538</t>
+          <t>152932</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>__69sIAJvNOfH1I8BBvxAc-</t>
+          <t>__6WRYQymo4NUk-yvxYsyOm</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
@@ -3646,42 +3951,47 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>高木, 律男</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-11-15T06:30:56Z</t>
+          <t>2025-11-16T13:55:57Z</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00005295']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033389']</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>['envir', 'geo']</t>
+          <t>['socio', 'scipo']</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>50052</t>
+          <t>176115</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>__6eh6fK9w5fvSFYqyPpqT1</t>
+          <t>__6Zc9eDyh_Ore1S5M7orcx</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
@@ -3698,42 +4008,47 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>平, 将志</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-11-17T00:11:13Z</t>
+          <t>2025-11-17T03:24:52Z</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007575']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>['anthro-se', 'demo']</t>
+          <t>['info', 'lang']</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>56125</t>
+          <t>152928</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>56125</t>
+          <t>152928</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>__6nBzfOPSAm5uMLhNxjadi</t>
+          <t>__6d3nTaXut5TIKehK6SmTD</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
@@ -3750,42 +4065,47 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>野村, 務</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-11-17T03:24:52Z</t>
+          <t>2025-11-15T06:30:56Z</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00025908']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00005295']</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>['info', 'lang']</t>
+          <t>['envir', 'geo']</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>152928</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>152928</t>
+          <t>50052</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>__6d3nTaXut5TIKehK6SmTD</t>
+          <t>__6eh6fK9w5fvSFYqyPpqT1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
@@ -3802,42 +4122,47 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>早川, 岳英</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-11-16T13:55:57Z</t>
+          <t>2025-11-15T19:24:54Z</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00033389']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031965']</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>['socio', 'scipo']</t>
+          <t>['edu', 'socio']</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>176115</t>
+          <t>70783</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>176115</t>
+          <t>70783</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>__6Zc9eDyh_Ore1S5M7orcx</t>
+          <t>__6n9RxznJgXSa0AaBbdhvc</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -3854,24 +4179,29 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Abe, Kotaro</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-11-17T00:30:08Z</t>
+          <t>2025-11-17T00:11:13Z</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029741']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007575']</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>['edu', 'socio']</t>
+          <t>['anthro-se', 'demo']</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -3879,17 +4209,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>56125</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>65166</t>
+          <t>56125</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>__70K5bGGob0ONEJjX-vHkm</t>
+          <t>__6nBzfOPSAm5uMLhNxjadi</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -3906,19 +4236,24 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>坂井, 摂子</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-11-15T19:24:54Z</t>
+          <t>2025-11-17T00:30:08Z</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031965']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029741']</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3931,17 +4266,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>70783</t>
+          <t>65166</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70783</t>
+          <t>65166</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>__6n9RxznJgXSa0AaBbdhvc</t>
+          <t>__70K5bGGob0ONEJjX-vHkm</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -3958,42 +4293,47 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>中村, 高康</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-11-15T19:30:48Z</t>
+          <t>2025-11-15T06:26:06Z</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030051']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028261']</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>['hist', 'scipo']</t>
+          <t>['envir', 'socio']</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>66163</t>
+          <t>162336</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>66163</t>
+          <t>162336</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>__7Du7t5QF80wBZifDx0uAi</t>
+          <t>__76of_e8KAQBwyM8tcUky0</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -4010,24 +4350,29 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Napat, Kamthonsiriwimol</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2025-11-15T06:26:06Z</t>
+          <t>2025-11-15T12:04:42Z</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028261']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017238']</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>['envir', 'socio']</t>
+          <t>['manag', 'eco']</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -4035,17 +4380,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>162336</t>
+          <t>107831</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>162336</t>
+          <t>107831</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>__76of_e8KAQBwyM8tcUky0</t>
+          <t>__7BqI8jmEgLJdBxpu0bvxK</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -4062,42 +4407,47 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>新海, 哲哉</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2025-11-15T12:04:42Z</t>
+          <t>2025-11-15T19:30:48Z</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00017238']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030051']</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>['manag', 'eco']</t>
+          <t>['hist', 'scipo']</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>66163</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>107831</t>
+          <t>66163</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>__7BqI8jmEgLJdBxpu0bvxK</t>
+          <t>__7Du7t5QF80wBZifDx0uAi</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
@@ -4114,24 +4464,29 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>飯長, 喜一郎</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2025-11-16T22:24:59Z</t>
+          <t>2025-11-17T02:09:54Z</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030009']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041902']</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>['psy', 'lang']</t>
+          <t>['info', 'museo']</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -4139,17 +4494,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>96419</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>96419</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>__7bsgFmFnetJSdKHzYLBLw</t>
+          <t>__7FKBPVIfNuLNNsB-sO5G7</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -4166,24 +4521,29 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>岡田, 伊策</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2025-11-17T02:09:54Z</t>
+          <t>2025-11-15T00:29:51Z</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00041902']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007343']</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>['info', 'museo']</t>
+          <t>['hist', 'litt']</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -4191,17 +4551,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>__7FKBPVIfNuLNNsB-sO5G7</t>
+          <t>__7Y1h5N0XyRubmaaMORku8</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -4218,24 +4578,29 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>田村, 優</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-11-15T00:29:51Z</t>
+          <t>2025-11-16T22:24:59Z</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00007343']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00030009']</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>['hist', 'litt']</t>
+          <t>['psy', 'lang']</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -4243,17 +4608,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>66035</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>55703</t>
+          <t>66035</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>__7Y1h5N0XyRubmaaMORku8</t>
+          <t>__7bsgFmFnetJSdKHzYLBLw</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -4270,42 +4635,47 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>武井, 澄江</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-11-17T00:30:08Z</t>
+          <t>2025-11-14T18:59:54Z</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029741']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00023197']</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>['edu', 'socio']</t>
+          <t>['psy', 'manag']</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>139939</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>65164</t>
+          <t>139939</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>__7ou-0gdZ_58qik1xpmlns</t>
+          <t>__7dpT72Z3Yra2c97TBUSTi</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
@@ -4322,24 +4692,29 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>屋形, 稔</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-11-16T05:22:57Z</t>
+          <t>2025-11-17T00:30:07Z</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00017470']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031315']</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>['socio', 'lang']</t>
+          <t>['manag', 'edu']</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -4347,17 +4722,17 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>110198</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>110198</t>
+          <t>123054</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>__7vu4EFkCZuimy74DAflCT</t>
+          <t>__7hXt04rxyZ1Jv4jCA86Ae</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
@@ -4374,42 +4749,47 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>平沢, 和司</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-11-14T18:59:54Z</t>
+          <t>2025-11-17T00:30:08Z</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00023197']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029741']</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>['psy', 'manag']</t>
+          <t>['edu', 'socio']</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>139939</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>139939</t>
+          <t>65164</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>__7dpT72Z3Yra2c97TBUSTi</t>
+          <t>__7ou-0gdZ_58qik1xpmlns</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
@@ -4426,42 +4806,47 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>吉原, 惠子</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-11-14T21:35:20Z</t>
+          <t>2025-11-16T05:22:57Z</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027193']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00017470']</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>['hist', 'anthro-se']</t>
+          <t>['socio', 'lang']</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>110198</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>110198</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>__8FxB9t6V37jk0cLUUgSnQ</t>
+          <t>__7vu4EFkCZuimy74DAflCT</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -4478,42 +4863,47 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>千葉, 正司</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2025-11-15T00:33:28Z</t>
+          <t>2025-11-14T18:26:43Z</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003641']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001808']</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>['envir', 'archi']</t>
+          <t>['info']</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>44266</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>__8i-7Rp2G8HbMGRfW_yukL</t>
+          <t>__8Flhoz6OMXpur0E-us2Td</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -4530,42 +4920,47 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Nakamura, Kazuki</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-11-14T18:26:43Z</t>
+          <t>2025-11-14T21:35:20Z</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00001808']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027193']</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>['info']</t>
+          <t>['hist', 'anthro-se']</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>59801</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>__8Flhoz6OMXpur0E-us2Td</t>
+          <t>__8FxB9t6V37jk0cLUUgSnQ</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
@@ -4582,42 +4977,47 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>友杉, 孝</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-11-17T00:30:07Z</t>
+          <t>2025-11-14T18:56:57Z</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031315']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028334']</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>['manag', 'edu']</t>
+          <t>['stat', 'envir']</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>123054</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>123054</t>
+          <t>68</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>__7hXt04rxyZ1Jv4jCA86Ae</t>
+          <t>__8e5MegHDrScXWfmGRaJaX</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -4634,42 +5034,47 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>児島, 清秀</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-11-17T00:30:08Z</t>
+          <t>2025-11-15T00:33:28Z</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031315']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003641']</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>['manag', 'edu']</t>
+          <t>['envir', 'archi']</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>123056</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>123056</t>
+          <t>44266</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>__8sQWvOdGzjsNUpM0TlLxV</t>
+          <t>__8i-7Rp2G8HbMGRfW_yukL</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
@@ -4686,42 +5091,47 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>五十嵐, 由利子</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-11-14T18:56:57Z</t>
+          <t>2025-11-17T00:30:08Z</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00028334']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031315']</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>['stat', 'envir']</t>
+          <t>['manag', 'edu']</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>123056</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>123056</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>__8e5MegHDrScXWfmGRaJaX</t>
+          <t>__8sQWvOdGzjsNUpM0TlLxV</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
@@ -4738,7 +5148,12 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>中村, 高康</t>
         </is>
       </c>
     </row>
@@ -4790,7 +5205,12 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>久保, 博子</t>
         </is>
       </c>
     </row>
@@ -4842,7 +5262,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Nishimoto, Kengo</t>
         </is>
       </c>
     </row>
@@ -4894,24 +5319,29 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>籏, 康之</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-11-14T22:17:26Z</t>
+          <t>2025-11-15T00:33:40Z</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027318']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003634']</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>['hisphilso', 'hist']</t>
+          <t>['hist', 'geo']</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -4919,17 +5349,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>44164</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>__9l5Gn7YBtdfwaj16Jr_qN</t>
+          <t>__96lXkoEUHpVhOgkoUMDEf</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
@@ -4946,7 +5376,12 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>大澤, 清二</t>
         </is>
       </c>
     </row>
@@ -4998,42 +5433,47 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>丹田, 桂太</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-11-15T00:33:40Z</t>
+          <t>2025-11-16T22:23:31Z</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003634']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054796']</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>['hist', 'geo']</t>
+          <t>['lang', 'musiq']</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>44164</t>
+          <t>163041</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>__96lXkoEUHpVhOgkoUMDEf</t>
+          <t>__9htbkvHgpb_BupOqt4_bt</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
@@ -5050,42 +5490,47 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>鎌田, 寧々</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2025-11-16T22:23:31Z</t>
+          <t>2025-11-14T22:17:26Z</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00054796']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00027318']</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>['lang', 'musiq']</t>
+          <t>['hisphilso', 'hist']</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>163041</t>
+          <t>60050</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>163041</t>
+          <t>60050</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>__9htbkvHgpb_BupOqt4_bt</t>
+          <t>__9l5Gn7YBtdfwaj16Jr_qN</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
@@ -5102,7 +5547,12 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>伊藤, 亜人</t>
         </is>
       </c>
     </row>
@@ -5154,42 +5604,47 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>柴田, 元幸</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2025-11-14T17:55:22Z</t>
+          <t>2025-11-14T18:59:54Z</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025544']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00023197']</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>['demo', 'envir']</t>
+          <t>['psy', 'manag']</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>55322</t>
+          <t>139938</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>55322</t>
+          <t>139938</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>__A1XUvYmq1KgPTIeaFkzqi</t>
+          <t>__9qmX_LIBa4jA-TEGNt5VY</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -5206,7 +5661,12 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>岡田, 正彦</t>
         </is>
       </c>
     </row>
@@ -5258,24 +5718,29 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>鈴木, 利光</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2025-11-15T00:33:28Z</t>
+          <t>2025-11-15T04:05:17Z</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003641']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031170']</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>['envir', 'archi']</t>
+          <t>['scipo', 'hist']</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -5283,17 +5748,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>68782</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>__A43DhYL_dQqp43FJ9pm6r</t>
+          <t>__9y6cAAUMQcGaF6rFz9Omz</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
@@ -5310,42 +5775,47 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>森田, 慎一郎</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2025-11-14T18:59:54Z</t>
+          <t>2025-11-14T17:55:22Z</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00023197']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025544']</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>['psy', 'manag']</t>
+          <t>['demo', 'envir']</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>139938</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>139938</t>
+          <t>55322</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>__9qmX_LIBa4jA-TEGNt5VY</t>
+          <t>__A1XUvYmq1KgPTIeaFkzqi</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -5362,24 +5832,29 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>箕輪, 光博</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2025-11-15T04:05:17Z</t>
+          <t>2025-11-15T00:33:28Z</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00031170']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003641']</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>['scipo', 'hist']</t>
+          <t>['envir', 'archi']</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -5387,17 +5862,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>68782</t>
+          <t>44272</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>__9y6cAAUMQcGaF6rFz9Omz</t>
+          <t>__A43DhYL_dQqp43FJ9pm6r</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
@@ -5414,7 +5889,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>水野, 由美</t>
         </is>
       </c>
     </row>
@@ -5466,42 +5946,47 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>近藤, 邦夫</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-11-14T22:50:35Z</t>
+          <t>2025-11-16T16:18:10Z</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025260']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051403']</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>['phil', 'art']</t>
+          <t>['scipo', 'socio']</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>153131</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>153131</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>__AX5fricOXHvMoNXk8b4W9</t>
+          <t>__AG14-pFQ-JF50KASNCVU8</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
@@ -5518,42 +6003,47 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>高木, 加奈絵</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-11-16T16:18:10Z</t>
+          <t>2025-11-15T00:33:28Z</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00051403']</t>
+          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003640']</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>['scipo', 'socio']</t>
+          <t>['envir', 'socio']</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>153131</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>153131</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>__AG14-pFQ-JF50KASNCVU8</t>
+          <t>__AG6mFfepQibk-DkvktVgM</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
@@ -5570,42 +6060,47 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>磯田, 憲生</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-11-15T00:33:28Z</t>
+          <t>2025-11-14T21:57:53Z</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>['ftniigatauniv:oai:niigata-u.repo.nii.ac.jp:00003640']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037298']</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>['envir', 'socio']</t>
+          <t>['litt', 'lang']</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>136402</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>136402</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>__AG6mFfepQibk-DkvktVgM</t>
+          <t>__AJQBO7M0TFNcrnFRaNTnd</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
@@ -5622,42 +6117,47 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>荒木, 純子</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-11-14T21:57:53Z</t>
+          <t>2025-11-14T22:50:35Z</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00037298']</t>
+          <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00025260']</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>['litt', 'lang']</t>
+          <t>['phil', 'art']</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>136402</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>136402</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>__AJQBO7M0TFNcrnFRaNTnd</t>
+          <t>__AX5fricOXHvMoNXk8b4W9</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
@@ -5674,7 +6174,12 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>not recovered</t>
+          <t>repository id</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>佐々木, 真二郎</t>
         </is>
       </c>
     </row>

--- a/data/output/authors_junk_names_elastic.xlsx
+++ b/data/output/authors_junk_names_elastic.xlsx
@@ -55,15 +55,15 @@
     <t>belongs_to</t>
   </si>
   <si>
+    <t>2025-11-15T14:20:59Z</t>
+  </si>
+  <si>
+    <t>2025-11-14T19:56:55Z</t>
+  </si>
+  <si>
     <t>2025-11-15T03:02:46Z</t>
   </si>
   <si>
-    <t>2025-11-15T14:20:59Z</t>
-  </si>
-  <si>
-    <t>2025-11-14T19:56:55Z</t>
-  </si>
-  <si>
     <t>2026-06-17T18:46:10Z</t>
   </si>
   <si>
@@ -82,66 +82,66 @@
     <t>2026-06-17T22:43:35Z</t>
   </si>
   <si>
+    <t>2026-08-04T04:55:25Z</t>
+  </si>
+  <si>
+    <t>2026-09-01T02:17:13Z</t>
+  </si>
+  <si>
+    <t>2026-06-17T19:14:24Z</t>
+  </si>
+  <si>
+    <t>2026-07-16T15:26:02Z</t>
+  </si>
+  <si>
+    <t>2026-07-08T00:16:02Z</t>
+  </si>
+  <si>
+    <t>2026-06-13T11:04:18Z</t>
+  </si>
+  <si>
+    <t>2026-07-29T13:05:25Z</t>
+  </si>
+  <si>
+    <t>2025-11-05T10:38:10Z</t>
+  </si>
+  <si>
+    <t>2026-03-09T11:00:17Z</t>
+  </si>
+  <si>
     <t>2026-03-09T20:09:38Z</t>
   </si>
   <si>
-    <t>2026-03-09T11:00:17Z</t>
-  </si>
-  <si>
-    <t>2026-08-04T04:55:25Z</t>
-  </si>
-  <si>
-    <t>2026-06-17T19:14:24Z</t>
-  </si>
-  <si>
-    <t>2026-09-01T02:17:13Z</t>
-  </si>
-  <si>
-    <t>2026-07-08T00:16:02Z</t>
-  </si>
-  <si>
     <t>2025-11-05T10:38:09Z</t>
   </si>
   <si>
-    <t>2026-06-13T11:04:18Z</t>
-  </si>
-  <si>
-    <t>2025-11-05T10:38:10Z</t>
-  </si>
-  <si>
     <t>2026-03-10T14:29:11Z</t>
   </si>
   <si>
     <t>2026-03-10T08:42:36Z</t>
   </si>
   <si>
+    <t>2025-11-05T10:38:59Z</t>
+  </si>
+  <si>
+    <t>2026-06-18T11:33:52Z</t>
+  </si>
+  <si>
+    <t>2026-07-10T09:05:57Z</t>
+  </si>
+  <si>
+    <t>2026-03-10T08:15:12Z</t>
+  </si>
+  <si>
+    <t>2025-11-05T10:38:16Z</t>
+  </si>
+  <si>
+    <t>2026-06-17T19:09:58Z</t>
+  </si>
+  <si>
     <t>2026-06-07T10:33:42Z</t>
   </si>
   <si>
-    <t>2026-06-18T11:33:52Z</t>
-  </si>
-  <si>
-    <t>2025-11-05T10:38:59Z</t>
-  </si>
-  <si>
-    <t>2026-07-29T13:05:25Z</t>
-  </si>
-  <si>
-    <t>2026-07-10T09:05:57Z</t>
-  </si>
-  <si>
-    <t>2026-03-10T08:15:12Z</t>
-  </si>
-  <si>
-    <t>2025-11-05T10:38:16Z</t>
-  </si>
-  <si>
-    <t>2026-06-17T19:09:58Z</t>
-  </si>
-  <si>
-    <t>2026-07-16T15:26:02Z</t>
-  </si>
-  <si>
     <t>2025-11-15T12:04:28Z</t>
   </si>
   <si>
@@ -682,13 +682,16 @@
     <t>2025-11-15T19:24:30Z</t>
   </si>
   <si>
+    <t>['ftnctuniv:oai:ir.nctu.edu.tw:11536_63071']</t>
+  </si>
+  <si>
+    <t>['ftdoajarticles:oai:doaj.org_article:cbe415714bb341009a450266a64982b6']</t>
+  </si>
+  <si>
     <t>['ftdavidrumseyc:oai:N_A:RUMSEY~8~1~337492~90105339']</t>
   </si>
   <si>
-    <t>['ftnctuniv:oai:ir.nctu.edu.tw:11536_63071']</t>
-  </si>
-  <si>
-    <t>['ftdoajarticles:oai:doaj.org_article:cbe415714bb341009a450266a64982b6']</t>
+    <t>['ftunibolognairis:oai:cris.unibo.it:11585_743243', 'ftdoajarticles:oai:doaj.org_article:cbe415714bb341009a450266a64982b6']</t>
   </si>
   <si>
     <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-102843695']</t>
@@ -700,69 +703,66 @@
     <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100235739']</t>
   </si>
   <si>
-    <t>['ftunibolognairis:oai:cris.unibo.it:11585_743243', 'ftdoajarticles:oai:doaj.org_article:cbe415714bb341009a450266a64982b6']</t>
-  </si>
-  <si>
     <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-102316754']</t>
   </si>
   <si>
     <t>['ftunivromairis:oai:iris.uniroma1.it:11573_1509595']</t>
   </si>
   <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-102829124']</t>
+  </si>
+  <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667']</t>
+  </si>
+  <si>
+    <t>['ftnorthwestusl:oai:scholarlycommons.law.northwestern.edu:njtip_symposium-1019']</t>
+  </si>
+  <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100851932']</t>
+  </si>
+  <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100239766']</t>
+  </si>
+  <si>
+    <t>['ftdergipark2ojs:oai:dergipark.org.tr:article_1502577']</t>
+  </si>
+  <si>
+    <t>['fttunivcrete:oai:dlib.tuc.gr:47531']</t>
+  </si>
+  <si>
+    <t>['fttunivcrete:oai:dlib.tuc.gr:58833']</t>
+  </si>
+  <si>
     <t>['fttunivcrete:oai:dlib.tuc.gr:54156']</t>
   </si>
   <si>
-    <t>['fttunivcrete:oai:dlib.tuc.gr:58833']</t>
-  </si>
-  <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-102829124']</t>
-  </si>
-  <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667']</t>
-  </si>
-  <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100851932']</t>
-  </si>
-  <si>
-    <t>['fttunivcrete:oai:dlib.tuc.gr:47531']</t>
-  </si>
-  <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100239766']</t>
-  </si>
-  <si>
     <t>['fttunivcrete:oai:dlib.tuc.gr:96320']</t>
   </si>
   <si>
     <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-007446622']</t>
   </si>
   <si>
+    <t>['fttunivcrete:oai:dlib.tuc.gr:85336']</t>
+  </si>
+  <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100236954']</t>
+  </si>
+  <si>
+    <t>['oai:library.oapen.org:20.500.12657_112677']</t>
+  </si>
+  <si>
+    <t>['fttunivcrete:oai:dlib.tuc.gr:74159']</t>
+  </si>
+  <si>
+    <t>['fttunivcrete:oai:dlib.tuc.gr:52197']</t>
+  </si>
+  <si>
+    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667', 'ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667']</t>
+  </si>
+  <si>
     <t>['oai:library.oapen.org:20.500.12657_112633', 'ftoapen:oai:library.oapen.org:20.500.12657_112633']</t>
   </si>
   <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-100236954']</t>
-  </si>
-  <si>
-    <t>['fttunivcrete:oai:dlib.tuc.gr:85336']</t>
-  </si>
-  <si>
-    <t>['ftdergipark2ojs:oai:dergipark.org.tr:article_1502577']</t>
-  </si>
-  <si>
-    <t>['oai:library.oapen.org:20.500.12657_112677']</t>
-  </si>
-  <si>
-    <t>['fttunivcrete:oai:dlib.tuc.gr:74159']</t>
-  </si>
-  <si>
-    <t>['fttunivcrete:oai:dlib.tuc.gr:52197']</t>
-  </si>
-  <si>
-    <t>['ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667', 'ftumichgbhathi:oai:quod.lib.umich.edu:MIU01-101686667']</t>
-  </si>
-  <si>
-    <t>['ftnorthwestusl:oai:scholarlycommons.law.northwestern.edu:njtip_symposium-1019']</t>
-  </si>
-  <si>
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00032435']</t>
   </si>
   <si>
@@ -1477,13 +1477,16 @@
     <t>['ftunivtokyo:oai:repository.dl.itc.u-tokyo.ac.jp:00029983']</t>
   </si>
   <si>
+    <t>['manag', 'eco']</t>
+  </si>
+  <si>
+    <t>['socio', 'demo']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
-    <t>['manag', 'eco']</t>
-  </si>
-  <si>
-    <t>['socio', 'demo']</t>
+    <t>['demo', 'envir', 'socio']</t>
   </si>
   <si>
     <t>['class', 'litt']</t>
@@ -1495,57 +1498,54 @@
     <t>['archi']</t>
   </si>
   <si>
-    <t>['demo', 'envir', 'socio']</t>
-  </si>
-  <si>
     <t>['info']</t>
   </si>
   <si>
     <t>['edu', 'psy']</t>
   </si>
   <si>
+    <t>['art', 'litt']</t>
+  </si>
+  <si>
+    <t>['art']</t>
+  </si>
+  <si>
+    <t>['droit', 'info']</t>
+  </si>
+  <si>
+    <t>['class']</t>
+  </si>
+  <si>
+    <t>['edu', 'info']</t>
+  </si>
+  <si>
+    <t>['info', 'demo', 'phil', 'edu']</t>
+  </si>
+  <si>
+    <t>['info', 'droit']</t>
+  </si>
+  <si>
     <t>['info', 'envir']</t>
   </si>
   <si>
-    <t>['info', 'droit']</t>
-  </si>
-  <si>
-    <t>['art', 'litt']</t>
-  </si>
-  <si>
-    <t>['art']</t>
-  </si>
-  <si>
-    <t>['info', 'demo', 'phil', 'edu']</t>
-  </si>
-  <si>
-    <t>['class']</t>
-  </si>
-  <si>
     <t>['eco', 'envir']</t>
   </si>
   <si>
     <t>['hist', 'hisphilso']</t>
   </si>
   <si>
+    <t>['lang', 'litt']</t>
+  </si>
+  <si>
+    <t>['info', 'geo']</t>
+  </si>
+  <si>
+    <t>['archeo', 'geo']</t>
+  </si>
+  <si>
     <t>['hist', 'scipo']</t>
   </si>
   <si>
-    <t>['edu', 'info']</t>
-  </si>
-  <si>
-    <t>['lang', 'litt']</t>
-  </si>
-  <si>
-    <t>['info', 'geo']</t>
-  </si>
-  <si>
-    <t>['archeo', 'geo']</t>
-  </si>
-  <si>
-    <t>['droit', 'info']</t>
-  </si>
-  <si>
     <t>['geo', 'demo']</t>
   </si>
   <si>
@@ -1900,16 +1900,19 @@
     <t>['hisphilso', 'psy']</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>3</t>
   </si>
   <si>
     <t>Dante Alighieri, 1265-1321. De vulgari eloquentia. Italian. 1529. http://viaf.org/viaf/4668159477985727990005</t>
@@ -1921,9 +1924,6 @@
     <t>Vignola, 1507-1573. http://id.loc.gov/ities/names/n82222501 http://viaf.org/viaf/56637758</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>Phillips, , auctioneer. http://id.loc.gov/ities/names/n83132163 http://viaf.org/viaf/75227852</t>
   </si>
   <si>
@@ -1933,72 +1933,72 @@
     <t>2019 at Uppsala Universitet BIBSAM http://jnnp. bmj. com/ J Neurol Neurosurg Psychiatry: first published as 10. 1136/jnnp-2019-321496 on 5 October 2019. Downloaded from 8 Verboon C</t>
   </si>
   <si>
+    <t>Hunter, Aaron Burtis, 1854-1933, http://id.loc.gov/ities/names/no2010024138 former owner.</t>
+  </si>
+  <si>
+    <t>Bloemaert, Abraham, 1564-1651 http://id.loc.gov/ities/names/nr93052276 http://viaf.org/viaf/77114225</t>
+  </si>
+  <si>
+    <t>Sponsored by Northwestern Law School’s Master of Science in Law, a one-year Master’s degree in law for scientists and engineers. For more information, please visit: http://www.law.northwestern.edu/academics/degree-programs/msl</t>
+  </si>
+  <si>
+    <t>Bosse, Abraham, 1602-1676 http://id.loc.gov/ities/names/n82272447 http://viaf.org/viaf/61542289</t>
+  </si>
+  <si>
+    <t>Bocchi, Achille, 1488-1562 http://id.loc.gov/ities/names/n92057019 http://viaf.org/viaf/149878</t>
+  </si>
+  <si>
+    <t>Http://2024.brs.org.tr, Abstract Book Of 8th International Brain Research School 20 - 26 May 2024, Isparta /türkiye.</t>
+  </si>
+  <si>
+    <t>Aggelakis Dimitrios(http://users.isc.tuc.gr/~daggelakis)</t>
+  </si>
+  <si>
+    <t>Qiao Li, 1934-(http://viaf.org/viaf/112423839)</t>
+  </si>
+  <si>
+    <t>Moropoulou, A(http://viaf.org/viaf/305714749)</t>
+  </si>
+  <si>
     <t>Bakolas, A(http://viaf.org/viaf/305714756)</t>
   </si>
   <si>
-    <t>Qiao Li, 1934-(http://viaf.org/viaf/112423839)</t>
-  </si>
-  <si>
-    <t>Moropoulou, A(http://viaf.org/viaf/305714749)</t>
-  </si>
-  <si>
-    <t>Hunter, Aaron Burtis, 1854-1933, http://id.loc.gov/ities/names/no2010024138 former owner.</t>
-  </si>
-  <si>
-    <t>Bloemaert, Abraham, 1564-1651 http://id.loc.gov/ities/names/nr93052276 http://viaf.org/viaf/77114225</t>
-  </si>
-  <si>
-    <t>Bosse, Abraham, 1602-1676 http://id.loc.gov/ities/names/n82272447 http://viaf.org/viaf/61542289</t>
-  </si>
-  <si>
     <t>Αγγελακης Δημητριος(http://users.isc.tuc.gr/~daggelakis)</t>
   </si>
   <si>
-    <t>Bocchi, Achille, 1488-1562 http://id.loc.gov/ities/names/n92057019 http://viaf.org/viaf/149878</t>
-  </si>
-  <si>
-    <t>Aggelakis Dimitrios(http://users.isc.tuc.gr/~daggelakis)</t>
+    <t>Ακασιαδης Χαριλαος(http://users.isc.tuc.gr/~cakasiadis)</t>
   </si>
   <si>
     <t>Akasiadis Charilaos(http://users.isc.tuc.gr/~cakasiadis)</t>
   </si>
   <si>
-    <t>Ακασιαδης Χαριλαος(http://users.isc.tuc.gr/~cakasiadis)</t>
-  </si>
-  <si>
     <t>Macquarrie, Alan (Alan Denis), . http://id.loc.gov/ities/names/n85098805</t>
   </si>
   <si>
+    <t>Αλεβιζος Παναγιωτης(http://users.isc.tuc.gr/~palevizos)</t>
+  </si>
+  <si>
+    <t>Alevizos Panagiotis(http://users.isc.tuc.gr/~palevizos)</t>
+  </si>
+  <si>
+    <t>Dürer, Albrecht, 1471-1528 http://id.loc.gov/ities/names/n79118011 http://viaf.org/viaf/54146999</t>
+  </si>
+  <si>
+    <t>Troy L. Cox - http://.org/0000-0001-9379-5102, Alan V. Brown - http://.org/0000-0003-0144-4722,Margaret E. Malone - http://.org/0000-0001-9640-412X</t>
+  </si>
+  <si>
+    <t>Artikis, Alexander(http://viaf.org/viaf/43834206)</t>
+  </si>
+  <si>
+    <t>Sarris, Alexander(http://viaf.org/viaf/19743442)</t>
+  </si>
+  <si>
+    <t>Browne, Alexander, active 1660-1677 http://id.loc.gov/ities/names/n85035349 http://viaf.org/viaf/22988134</t>
+  </si>
+  <si>
     <t>Ayyad , Ahmad | http://.org/0009-0007-2829-2382</t>
   </si>
   <si>
-    <t>Dürer, Albrecht, 1471-1528 http://id.loc.gov/ities/names/n79118011 http://viaf.org/viaf/54146999</t>
-  </si>
-  <si>
-    <t>Αλεβιζος Παναγιωτης(http://users.isc.tuc.gr/~palevizos)</t>
-  </si>
-  <si>
-    <t>Http://2024.brs.org.tr, Abstract Book Of 8th International Brain Research School 20 - 26 May 2024, Isparta /türkiye.</t>
-  </si>
-  <si>
-    <t>Alevizos Panagiotis(http://users.isc.tuc.gr/~palevizos)</t>
-  </si>
-  <si>
-    <t>Troy L. Cox - http://.org/0000-0001-9379-5102, Alan V. Brown - http://.org/0000-0003-0144-4722,Margaret E. Malone - http://.org/0000-0001-9640-412X</t>
-  </si>
-  <si>
-    <t>Artikis, Alexander(http://viaf.org/viaf/43834206)</t>
-  </si>
-  <si>
-    <t>Sarris, Alexander(http://viaf.org/viaf/19743442)</t>
-  </si>
-  <si>
-    <t>Browne, Alexander, active 1660-1677 http://id.loc.gov/ities/names/n85035349 http://viaf.org/viaf/22988134</t>
-  </si>
-  <si>
-    <t>Sponsored by Northwestern Law School’s Master of Science in Law, a one-year Master’s degree in law for scientists and engineers. For more information, please visit: http://www.law.northwestern.edu/academics/degree-programs/msl</t>
-  </si>
-  <si>
     <t>123598</t>
   </si>
   <si>
@@ -3415,82 +3415,85 @@
     <t>2019 At Uppsala Universitet Bibsam  Bmj. Com  J Neurol Neurosurg Psychiatry  First Published As 10. 1136 Jnnp-2019-321496 On 5 October 2019. Downloaded From 8 Verboon C</t>
   </si>
   <si>
+    <t>Hunter, Aaron Burtis, 1854-1933,  Former Owner.</t>
+  </si>
+  <si>
+    <t>Bloemaert, Abraham, 1564-1651</t>
+  </si>
+  <si>
+    <t>Sponsored By Northwestern Law School’S Master Of Science In Law, A One-Year Master’S Degree In Law For Scientists And Engineers. For More Information, Please Visit</t>
+  </si>
+  <si>
+    <t>Bosse, Abraham, 1602-1676</t>
+  </si>
+  <si>
+    <t>Bocchi, Achille, 1488-1562</t>
+  </si>
+  <si>
+    <t>Http 2024.Brs.Org.Tr, Abstract Book Of 8Th International Brain Research School 20 - 26 May 2024, Isparta  Türkiye.</t>
+  </si>
+  <si>
+    <t>Aggelakis Dimitrios(</t>
+  </si>
+  <si>
+    <t>Qiao Li, 1934-(</t>
+  </si>
+  <si>
+    <t>Moropoulou, A(</t>
+  </si>
+  <si>
     <t>Bakolas, A(</t>
   </si>
   <si>
-    <t>Qiao Li, 1934-(</t>
-  </si>
-  <si>
-    <t>Moropoulou, A(</t>
-  </si>
-  <si>
-    <t>Hunter, Aaron Burtis, 1854-1933,  Former Owner.</t>
-  </si>
-  <si>
-    <t>Bloemaert, Abraham, 1564-1651</t>
-  </si>
-  <si>
-    <t>Bosse, Abraham, 1602-1676</t>
-  </si>
-  <si>
     <t>Αγγελακης Δημητριος(</t>
   </si>
   <si>
-    <t>Bocchi, Achille, 1488-1562</t>
-  </si>
-  <si>
-    <t>Aggelakis Dimitrios(</t>
+    <t>Ακασιαδης Χαριλαος(</t>
   </si>
   <si>
     <t>Akasiadis Charilaos(</t>
   </si>
   <si>
-    <t>Ακασιαδης Χαριλαος(</t>
-  </si>
-  <si>
     <t>Macquarrie, Alan (Alan Denis), .</t>
   </si>
   <si>
+    <t>Αλεβιζος Παναγιωτης(</t>
+  </si>
+  <si>
+    <t>Alevizos Panagiotis(</t>
+  </si>
+  <si>
+    <t>DüRer, Albrecht, 1471-1528</t>
+  </si>
+  <si>
+    <t>Troy L. Cox</t>
+  </si>
+  <si>
+    <t>Artikis, Alexander(</t>
+  </si>
+  <si>
+    <t>Sarris, Alexander(</t>
+  </si>
+  <si>
+    <t>Browne, Alexander, Active 1660-1677</t>
+  </si>
+  <si>
     <t>Ahmad Ayyad</t>
   </si>
   <si>
-    <t>DüRer, Albrecht, 1471-1528</t>
-  </si>
-  <si>
-    <t>Αλεβιζος Παναγιωτης(</t>
-  </si>
-  <si>
-    <t>Http 2024.Brs.Org.Tr, Abstract Book Of 8Th International Brain Research School 20 - 26 May 2024, Isparta  Türkiye.</t>
-  </si>
-  <si>
-    <t>Alevizos Panagiotis(</t>
-  </si>
-  <si>
-    <t>Troy L. Cox</t>
-  </si>
-  <si>
-    <t>Artikis, Alexander(</t>
-  </si>
-  <si>
-    <t>Sarris, Alexander(</t>
-  </si>
-  <si>
-    <t>Browne, Alexander, Active 1660-1677</t>
-  </si>
-  <si>
-    <t>Sponsored By Northwestern Law School’S Master Of Science In Law, A One-Year Master’S Degree In Law For Scientists And Engineers. For More Information, Please Visit</t>
+    <t>__Qb6dhGCuSF8a_Zyxy01hJ</t>
+  </si>
+  <si>
+    <t>__Lf3PykJx4L9-dTyQMzBbm</t>
+  </si>
+  <si>
+    <t>__oC9E7cVS7fOxYjgW1atqq</t>
   </si>
   <si>
     <t>__rYNuWw1igYZC1D8Zc0ebE</t>
   </si>
   <si>
-    <t>__Lf3PykJx4L9-dTyQMzBbm</t>
-  </si>
-  <si>
-    <t>__Qb6dhGCuSF8a_Zyxy01hJ</t>
-  </si>
-  <si>
-    <t>__oC9E7cVS7fOxYjgW1atqq</t>
+    <t>__e6hWqSg7_qiy0-u-Y4F8J</t>
   </si>
   <si>
     <t>_de_vulgari_eloquentia_italian_http_viaf_org_viaf_dante_alighieri_1qjOi8VRcChBfdjgLHEvW</t>
@@ -3502,9 +3505,6 @@
     <t>_http_id_loc_gov_ities_names_n_http_viaf_org_viaf_vignola_4a9lrp9xVMnfJnEld9bIm</t>
   </si>
   <si>
-    <t>__e6hWqSg7_qiy0-u-Y4F8J</t>
-  </si>
-  <si>
     <t>_phillips_xL_mm5joH8RR8NN9FwRss</t>
   </si>
   <si>
@@ -3514,75 +3514,75 @@
     <t>_at_uppsala_universitet_bibsam_http_jnnp_bmj_com_j_neurol_neurosurg_psychiatry_first_published_as_jnnp_on_october_downloaded_from_verboon_c_RuaF0aB-PREMU0qSv6bqi</t>
   </si>
   <si>
+    <t>aaron_burtis_hunter_5-uNyPpE5Chfzp3N6hX2K</t>
+  </si>
+  <si>
+    <t>aaron_burtis_hunter__F094Vs8Kn3yYvsbsz5Rb</t>
+  </si>
+  <si>
+    <t>abraham_bloemaert_oZ6C8dT3gphESC3accfhB</t>
+  </si>
+  <si>
+    <t>a_one_year_master_s_degree_in_law_for_scientists_and_engineers_for_more_information_sponsored_by_northwestern_law_school_s_master_of_science_in_law_8efEG1i5djhXfS0SKuS-l</t>
+  </si>
+  <si>
+    <t>abraham_bosse_zUWLzd5Tzlo6G31QJWjpS</t>
+  </si>
+  <si>
+    <t>achille_bocchi_UqHriJVSjpVKFq_wiX5Ft</t>
+  </si>
+  <si>
+    <t>abstract_book_of_th_international_brain_research_school_may_http_brs_org_tr_0rM1E8eCsvR_nWDwnb6vS</t>
+  </si>
+  <si>
+    <t>aggelakis_dimitrios_http_usersisctucgr_daggelakis__jIc5BseH9b-LU4DEaS0ba</t>
+  </si>
+  <si>
+    <t>_http_viaf_org_viaf_qiao_li_bk7_1hQX8nv0OwhQOMk3Q</t>
+  </si>
+  <si>
+    <t>a_http_viaf_org_viaf_moropoulou_8vc8YnjwfWJSOjaMqXu6D</t>
+  </si>
+  <si>
     <t>a_http_viaf_org_viaf_bakolas_0GqmLcGsS7C7WLSL3Uqb-</t>
   </si>
   <si>
-    <t>_http_viaf_org_viaf_qiao_li_bk7_1hQX8nv0OwhQOMk3Q</t>
-  </si>
-  <si>
-    <t>a_http_viaf_org_viaf_moropoulou_8vc8YnjwfWJSOjaMqXu6D</t>
-  </si>
-  <si>
-    <t>aaron_burtis_hunter_5-uNyPpE5Chfzp3N6hX2K</t>
-  </si>
-  <si>
-    <t>abraham_bloemaert_oZ6C8dT3gphESC3accfhB</t>
-  </si>
-  <si>
-    <t>aaron_burtis_hunter__F094Vs8Kn3yYvsbsz5Rb</t>
-  </si>
-  <si>
-    <t>abraham_bosse_zUWLzd5Tzlo6G31QJWjpS</t>
-  </si>
-  <si>
     <t>aggelakes_demetrios_http_usersisctucgr_daggelakis__XaAsKWahng05KEm2pWq5M</t>
   </si>
   <si>
-    <t>achille_bocchi_UqHriJVSjpVKFq_wiX5Ft</t>
-  </si>
-  <si>
-    <t>aggelakis_dimitrios_http_usersisctucgr_daggelakis__jIc5BseH9b-LU4DEaS0ba</t>
+    <t>akasiades_kharilaos_http_usersisctucgr_cakasiadis__IgSIifR7F6n5pt5ZrNEmB</t>
   </si>
   <si>
     <t>akasiadis_charilaos_http_usersisctucgr_cakasiadis__riy2zSfSLEPuWrGxmW39K</t>
   </si>
   <si>
-    <t>akasiades_kharilaos_http_usersisctucgr_cakasiadis__IgSIifR7F6n5pt5ZrNEmB</t>
-  </si>
-  <si>
     <t>alan_alan_denis_macquarrie_LKNnU5RopnZ7OEIuOX_oO</t>
   </si>
   <si>
+    <t>alebizos_panagiotes_http_usersisctucgr_palevizos__dRBO8_6ZVWVnUYetze1Sk</t>
+  </si>
+  <si>
+    <t>alevizos_panagiotis_http_usersisctucgr_palevizos__iyh5iJoRgapvpC1Xi_No8</t>
+  </si>
+  <si>
+    <t>albrecht_durer_beP_z8DGp_ecqp2zvWIOL</t>
+  </si>
+  <si>
+    <t>alan_v_brown_http_org_troy_l_cox_http_org__C8vYqCZfeLBuEzh2HIDl0</t>
+  </si>
+  <si>
+    <t>alexander_http_viaf_org_viaf_artikis_GBrdqjHsf5aeL3_JWbdZX</t>
+  </si>
+  <si>
+    <t>alexander_http_viaf_org_viaf_sarris_T8gPE2F4bSlOQWScIWObS</t>
+  </si>
+  <si>
+    <t>alexander_browne_kCJZhQLRS66FZrQCsYyvq</t>
+  </si>
+  <si>
     <t>ahmad_http_org_ayyad_tXusKa1yR1zW6CupaZJMG</t>
   </si>
   <si>
-    <t>albrecht_durer_beP_z8DGp_ecqp2zvWIOL</t>
-  </si>
-  <si>
-    <t>alebizos_panagiotes_http_usersisctucgr_palevizos__dRBO8_6ZVWVnUYetze1Sk</t>
-  </si>
-  <si>
-    <t>abstract_book_of_th_international_brain_research_school_may_http_brs_org_tr_0rM1E8eCsvR_nWDwnb6vS</t>
-  </si>
-  <si>
-    <t>alevizos_panagiotis_http_usersisctucgr_palevizos__iyh5iJoRgapvpC1Xi_No8</t>
-  </si>
-  <si>
-    <t>alan_v_brown_http_org_troy_l_cox_http_org__C8vYqCZfeLBuEzh2HIDl0</t>
-  </si>
-  <si>
-    <t>alexander_http_viaf_org_viaf_artikis_GBrdqjHsf5aeL3_JWbdZX</t>
-  </si>
-  <si>
-    <t>alexander_http_viaf_org_viaf_sarris_T8gPE2F4bSlOQWScIWObS</t>
-  </si>
-  <si>
-    <t>alexander_browne_kCJZhQLRS66FZrQCsYyvq</t>
-  </si>
-  <si>
-    <t>a_one_year_master_s_degree_in_law_for_scientists_and_engineers_for_more_information_sponsored_by_northwestern_law_school_s_master_of_science_in_law_8efEG1i5djhXfS0SKuS-l</t>
-  </si>
-  <si>
     <t>__-76q-D_tyR-oRhWq8F96z</t>
   </si>
   <si>
@@ -4981,10 +4981,10 @@
     <t>__zp9Yp5_EPKG_1b2bcs4gK</t>
   </si>
   <si>
+    <t>0000-0001-9379-5102</t>
+  </si>
+  <si>
     <t>0009-0007-2829-2382</t>
-  </si>
-  <si>
-    <t>0000-0001-9379-5102</t>
   </si>
   <si>
     <t>numeric</t>
@@ -6570,13 +6570,13 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -6675,7 +6675,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>225</v>
@@ -6684,33 +6684,33 @@
         <v>490</v>
       </c>
       <c r="D6">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
         <v>632</v>
       </c>
       <c r="F6" t="s">
-        <v>1127</v>
+        <v>632</v>
       </c>
       <c r="G6" t="s">
         <v>1159</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="L6" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>226</v>
@@ -6719,13 +6719,13 @@
         <v>491</v>
       </c>
       <c r="D7">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
         <v>633</v>
       </c>
       <c r="F7" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G7" t="s">
         <v>1160</v>
@@ -6745,7 +6745,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
         <v>227</v>
@@ -6754,13 +6754,13 @@
         <v>492</v>
       </c>
       <c r="D8">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
         <v>634</v>
       </c>
       <c r="F8" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G8" t="s">
         <v>1161</v>
@@ -6780,7 +6780,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
         <v>228</v>
@@ -6789,28 +6789,28 @@
         <v>493</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
         <v>635</v>
       </c>
       <c r="F9" t="s">
-        <v>635</v>
+        <v>1129</v>
       </c>
       <c r="G9" t="s">
         <v>1162</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="L9" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -6853,10 +6853,10 @@
         <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C11" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D11">
         <v>87</v>
@@ -6929,7 +6929,7 @@
         <v>496</v>
       </c>
       <c r="D13">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>639</v>
@@ -6958,19 +6958,19 @@
         <v>23</v>
       </c>
       <c r="B14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C14" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D14">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="F14" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="G14" t="s">
         <v>1167</v>
@@ -6990,22 +6990,22 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C15" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E15" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="F15" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="G15" t="s">
         <v>1168</v>
@@ -7025,7 +7025,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s">
         <v>233</v>
@@ -7034,13 +7034,13 @@
         <v>498</v>
       </c>
       <c r="D16">
-        <v>89</v>
+        <v>226</v>
       </c>
       <c r="E16" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="F16" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="G16" t="s">
         <v>1169</v>
@@ -7060,22 +7060,22 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
         <v>234</v>
       </c>
       <c r="C17" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
       <c r="D17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E17" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="F17" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="G17" t="s">
         <v>1170</v>
@@ -7095,22 +7095,22 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C18" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D18">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E18" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="F18" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="G18" t="s">
         <v>1171</v>
@@ -7130,16 +7130,16 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B19" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C19" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="D19">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
         <v>644</v>
@@ -7165,13 +7165,13 @@
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C20" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="D20">
         <v>56</v>
@@ -7200,16 +7200,16 @@
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C21" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D21">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="E21" t="s">
         <v>646</v>
@@ -7235,16 +7235,16 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B22" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C22" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="D22">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E22" t="s">
         <v>647</v>
@@ -7273,13 +7273,13 @@
         <v>31</v>
       </c>
       <c r="B23" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C23" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D23">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
         <v>648</v>
@@ -7305,16 +7305,16 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D24">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E24" t="s">
         <v>649</v>
@@ -7340,16 +7340,16 @@
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C25" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D25">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E25" t="s">
         <v>650</v>
@@ -7384,7 +7384,7 @@
         <v>504</v>
       </c>
       <c r="D26">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E26" t="s">
         <v>651</v>
@@ -7395,20 +7395,17 @@
       <c r="G26" t="s">
         <v>1179</v>
       </c>
-      <c r="H26" t="s">
-        <v>1655</v>
-      </c>
       <c r="I26">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="L26" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -7419,10 +7416,10 @@
         <v>241</v>
       </c>
       <c r="C27" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D27">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="E27" t="s">
         <v>652</v>
@@ -7483,16 +7480,16 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
       <c r="D29">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="E29" t="s">
         <v>654</v>
@@ -7518,16 +7515,16 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C30" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="D30">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="E30" t="s">
         <v>655</v>
@@ -7574,7 +7571,7 @@
         <v>1184</v>
       </c>
       <c r="H31" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="I31">
         <v>1</v>
@@ -7667,7 +7664,7 @@
         <v>247</v>
       </c>
       <c r="C34" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D34">
         <v>105</v>
@@ -7705,7 +7702,7 @@
         <v>509</v>
       </c>
       <c r="D35">
-        <v>226</v>
+        <v>47</v>
       </c>
       <c r="E35" t="s">
         <v>660</v>
@@ -7716,17 +7713,20 @@
       <c r="G35" t="s">
         <v>1188</v>
       </c>
+      <c r="H35" t="s">
+        <v>1656</v>
+      </c>
       <c r="I35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J35" t="b">
         <v>0</v>
       </c>
       <c r="K35" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="L35" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -7927,7 +7927,7 @@
         <v>254</v>
       </c>
       <c r="C41" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D41">
         <v>6</v>
@@ -8079,7 +8079,7 @@
         <v>254</v>
       </c>
       <c r="C45" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D45">
         <v>6</v>
@@ -8497,7 +8497,7 @@
         <v>267</v>
       </c>
       <c r="C56" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D56">
         <v>6</v>
@@ -8573,7 +8573,7 @@
         <v>269</v>
       </c>
       <c r="C58" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D58">
         <v>5</v>
@@ -9105,7 +9105,7 @@
         <v>281</v>
       </c>
       <c r="C72" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D72">
         <v>5</v>
@@ -10017,7 +10017,7 @@
         <v>302</v>
       </c>
       <c r="C96" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D96">
         <v>6</v>
@@ -10055,7 +10055,7 @@
         <v>281</v>
       </c>
       <c r="C97" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D97">
         <v>5</v>
@@ -11005,7 +11005,7 @@
         <v>281</v>
       </c>
       <c r="C122" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D122">
         <v>5</v>
@@ -11613,7 +11613,7 @@
         <v>329</v>
       </c>
       <c r="C138" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D138">
         <v>6</v>
@@ -11841,7 +11841,7 @@
         <v>334</v>
       </c>
       <c r="C144" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="D144">
         <v>5</v>
@@ -11993,7 +11993,7 @@
         <v>337</v>
       </c>
       <c r="C148" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D148">
         <v>5</v>
@@ -12107,7 +12107,7 @@
         <v>339</v>
       </c>
       <c r="C151" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D151">
         <v>5</v>
@@ -12981,7 +12981,7 @@
         <v>355</v>
       </c>
       <c r="C174" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D174">
         <v>5</v>
@@ -13475,7 +13475,7 @@
         <v>254</v>
       </c>
       <c r="C187" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D187">
         <v>6</v>
@@ -13665,7 +13665,7 @@
         <v>364</v>
       </c>
       <c r="C192" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D192">
         <v>5</v>
@@ -14273,7 +14273,7 @@
         <v>281</v>
       </c>
       <c r="C208" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D208">
         <v>5</v>
@@ -14653,7 +14653,7 @@
         <v>254</v>
       </c>
       <c r="C218" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D218">
         <v>6</v>
@@ -14805,7 +14805,7 @@
         <v>269</v>
       </c>
       <c r="C222" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D222">
         <v>5</v>
@@ -15679,7 +15679,7 @@
         <v>254</v>
       </c>
       <c r="C245" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D245">
         <v>6</v>
@@ -16591,7 +16591,7 @@
         <v>302</v>
       </c>
       <c r="C269" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D269">
         <v>6</v>
@@ -17389,7 +17389,7 @@
         <v>254</v>
       </c>
       <c r="C290" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D290">
         <v>6</v>
@@ -17655,7 +17655,7 @@
         <v>411</v>
       </c>
       <c r="C297" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D297">
         <v>5</v>
@@ -20163,7 +20163,7 @@
         <v>434</v>
       </c>
       <c r="C363" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D363">
         <v>6</v>
@@ -20467,7 +20467,7 @@
         <v>364</v>
       </c>
       <c r="C371" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D371">
         <v>5</v>
@@ -20657,7 +20657,7 @@
         <v>254</v>
       </c>
       <c r="C376" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D376">
         <v>6</v>
@@ -21037,7 +21037,7 @@
         <v>254</v>
       </c>
       <c r="C386" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D386">
         <v>6</v>
@@ -21189,7 +21189,7 @@
         <v>440</v>
       </c>
       <c r="C390" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D390">
         <v>5</v>
@@ -21531,7 +21531,7 @@
         <v>254</v>
       </c>
       <c r="C399" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D399">
         <v>6</v>
@@ -21721,7 +21721,7 @@
         <v>446</v>
       </c>
       <c r="C404" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D404">
         <v>5</v>
@@ -22139,7 +22139,7 @@
         <v>453</v>
       </c>
       <c r="C415" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D415">
         <v>6</v>
@@ -22405,7 +22405,7 @@
         <v>455</v>
       </c>
       <c r="C422" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="D422">
         <v>5</v>
